--- a/archivos/tabla_temporadas.xlsx
+++ b/archivos/tabla_temporadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTICA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\172.10.18.128\info\archivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E249F90-8936-4C59-9E62-A70E507DFF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20734B7D-0C32-4A73-819F-46324EDB7B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -42,7 +42,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =Cosecha([@Columna1])</t>
@@ -57,7 +57,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -66,7 +66,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =MAYUSC(TEXTO([@Columna1];"mmm"))</t>
@@ -81,7 +81,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -90,7 +90,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =fechaSQL([@Columna1])</t>
@@ -105,7 +105,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -114,7 +114,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =Cosecha([@Columna1])</t>
@@ -129,7 +129,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -138,7 +138,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =TEXTO(K320;"mmmm")</t>
@@ -153,7 +153,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -162,7 +162,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =MAYUSC(TEXTO([@Columna1];"mmm"))</t>
@@ -177,7 +177,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -186,7 +186,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =fechaSQL([@Columna1])</t>
@@ -201,7 +201,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -210,7 +210,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =Cosecha([@Columna1])</t>
@@ -225,7 +225,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Hilder:</t>
         </r>
@@ -234,7 +234,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 =TEXTO(K320;"mmmm")</t>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="1600">
   <si>
     <t>cosecha</t>
   </si>
@@ -4121,6 +4121,942 @@
   </si>
   <si>
     <t>DI2653</t>
+  </si>
+  <si>
+    <t>EN2701</t>
+  </si>
+  <si>
+    <t>2027-1-7</t>
+  </si>
+  <si>
+    <t>EN2702</t>
+  </si>
+  <si>
+    <t>2027-1-14</t>
+  </si>
+  <si>
+    <t>EN2703</t>
+  </si>
+  <si>
+    <t>2027-1-21</t>
+  </si>
+  <si>
+    <t>EN2704</t>
+  </si>
+  <si>
+    <t>2027-1-28</t>
+  </si>
+  <si>
+    <t>FE2705</t>
+  </si>
+  <si>
+    <t>2027-2-4</t>
+  </si>
+  <si>
+    <t>FE2706</t>
+  </si>
+  <si>
+    <t>2027-2-11</t>
+  </si>
+  <si>
+    <t>FE2707</t>
+  </si>
+  <si>
+    <t>2027-2-18</t>
+  </si>
+  <si>
+    <t>FE2708</t>
+  </si>
+  <si>
+    <t>2027-2-25</t>
+  </si>
+  <si>
+    <t>MA2709</t>
+  </si>
+  <si>
+    <t>2027-3-4</t>
+  </si>
+  <si>
+    <t>MA2710</t>
+  </si>
+  <si>
+    <t>2027-3-11</t>
+  </si>
+  <si>
+    <t>MA2711</t>
+  </si>
+  <si>
+    <t>2027-3-18</t>
+  </si>
+  <si>
+    <t>MA2712</t>
+  </si>
+  <si>
+    <t>2027-3-25</t>
+  </si>
+  <si>
+    <t>AB2713</t>
+  </si>
+  <si>
+    <t>2027-4-1</t>
+  </si>
+  <si>
+    <t>AB2714</t>
+  </si>
+  <si>
+    <t>2027-4-8</t>
+  </si>
+  <si>
+    <t>AB2715</t>
+  </si>
+  <si>
+    <t>2027-4-15</t>
+  </si>
+  <si>
+    <t>AB2716</t>
+  </si>
+  <si>
+    <t>2027-4-22</t>
+  </si>
+  <si>
+    <t>AB2717</t>
+  </si>
+  <si>
+    <t>2027-4-29</t>
+  </si>
+  <si>
+    <t>MY2718</t>
+  </si>
+  <si>
+    <t>2027-5-6</t>
+  </si>
+  <si>
+    <t>MY2719</t>
+  </si>
+  <si>
+    <t>2027-5-13</t>
+  </si>
+  <si>
+    <t>MY2720</t>
+  </si>
+  <si>
+    <t>2027-5-20</t>
+  </si>
+  <si>
+    <t>MY2721</t>
+  </si>
+  <si>
+    <t>2027-5-27</t>
+  </si>
+  <si>
+    <t>JU2722</t>
+  </si>
+  <si>
+    <t>2027-6-3</t>
+  </si>
+  <si>
+    <t>JU2723</t>
+  </si>
+  <si>
+    <t>2027-6-10</t>
+  </si>
+  <si>
+    <t>JU2724</t>
+  </si>
+  <si>
+    <t>2027-6-17</t>
+  </si>
+  <si>
+    <t>JU2725</t>
+  </si>
+  <si>
+    <t>2027-6-24</t>
+  </si>
+  <si>
+    <t>JL2726</t>
+  </si>
+  <si>
+    <t>2027-7-1</t>
+  </si>
+  <si>
+    <t>JL2727</t>
+  </si>
+  <si>
+    <t>2027-7-8</t>
+  </si>
+  <si>
+    <t>JL2728</t>
+  </si>
+  <si>
+    <t>2027-7-15</t>
+  </si>
+  <si>
+    <t>JL2729</t>
+  </si>
+  <si>
+    <t>2027-7-22</t>
+  </si>
+  <si>
+    <t>JL2730</t>
+  </si>
+  <si>
+    <t>2027-7-29</t>
+  </si>
+  <si>
+    <t>AG2731</t>
+  </si>
+  <si>
+    <t>2027-8-5</t>
+  </si>
+  <si>
+    <t>AG2732</t>
+  </si>
+  <si>
+    <t>2027-8-12</t>
+  </si>
+  <si>
+    <t>AG2733</t>
+  </si>
+  <si>
+    <t>2027-8-19</t>
+  </si>
+  <si>
+    <t>AG2734</t>
+  </si>
+  <si>
+    <t>2027-8-26</t>
+  </si>
+  <si>
+    <t>SE2735</t>
+  </si>
+  <si>
+    <t>2027-9-2</t>
+  </si>
+  <si>
+    <t>SE2736</t>
+  </si>
+  <si>
+    <t>2027-9-9</t>
+  </si>
+  <si>
+    <t>SE2737</t>
+  </si>
+  <si>
+    <t>2027-9-16</t>
+  </si>
+  <si>
+    <t>SE2738</t>
+  </si>
+  <si>
+    <t>2027-9-23</t>
+  </si>
+  <si>
+    <t>SE2739</t>
+  </si>
+  <si>
+    <t>2027-9-30</t>
+  </si>
+  <si>
+    <t>OC2740</t>
+  </si>
+  <si>
+    <t>2027-10-7</t>
+  </si>
+  <si>
+    <t>OC2741</t>
+  </si>
+  <si>
+    <t>2027-10-14</t>
+  </si>
+  <si>
+    <t>OC2742</t>
+  </si>
+  <si>
+    <t>2027-10-21</t>
+  </si>
+  <si>
+    <t>OC2743</t>
+  </si>
+  <si>
+    <t>2027-10-28</t>
+  </si>
+  <si>
+    <t>NO2744</t>
+  </si>
+  <si>
+    <t>2027-11-4</t>
+  </si>
+  <si>
+    <t>NO2745</t>
+  </si>
+  <si>
+    <t>2027-11-11</t>
+  </si>
+  <si>
+    <t>NO2746</t>
+  </si>
+  <si>
+    <t>2027-11-18</t>
+  </si>
+  <si>
+    <t>NO2747</t>
+  </si>
+  <si>
+    <t>2027-11-25</t>
+  </si>
+  <si>
+    <t>DI2748</t>
+  </si>
+  <si>
+    <t>2027-12-2</t>
+  </si>
+  <si>
+    <t>DI2749</t>
+  </si>
+  <si>
+    <t>2027-12-9</t>
+  </si>
+  <si>
+    <t>DI2750</t>
+  </si>
+  <si>
+    <t>2027-12-16</t>
+  </si>
+  <si>
+    <t>DI2751</t>
+  </si>
+  <si>
+    <t>2027-12-23</t>
+  </si>
+  <si>
+    <t>DI2752</t>
+  </si>
+  <si>
+    <t>2027-12-30</t>
+  </si>
+  <si>
+    <t>EN2801</t>
+  </si>
+  <si>
+    <t>2028-1-6</t>
+  </si>
+  <si>
+    <t>EN2802</t>
+  </si>
+  <si>
+    <t>2028-1-13</t>
+  </si>
+  <si>
+    <t>EN2803</t>
+  </si>
+  <si>
+    <t>2028-1-20</t>
+  </si>
+  <si>
+    <t>EN2804</t>
+  </si>
+  <si>
+    <t>2028-1-27</t>
+  </si>
+  <si>
+    <t>FE2805</t>
+  </si>
+  <si>
+    <t>2028-2-3</t>
+  </si>
+  <si>
+    <t>FE2806</t>
+  </si>
+  <si>
+    <t>2028-2-10</t>
+  </si>
+  <si>
+    <t>FE2807</t>
+  </si>
+  <si>
+    <t>2028-2-17</t>
+  </si>
+  <si>
+    <t>FE2808</t>
+  </si>
+  <si>
+    <t>2028-2-24</t>
+  </si>
+  <si>
+    <t>MA2809</t>
+  </si>
+  <si>
+    <t>2028-3-2</t>
+  </si>
+  <si>
+    <t>MA2810</t>
+  </si>
+  <si>
+    <t>2028-3-9</t>
+  </si>
+  <si>
+    <t>MA2811</t>
+  </si>
+  <si>
+    <t>2028-3-16</t>
+  </si>
+  <si>
+    <t>MA2812</t>
+  </si>
+  <si>
+    <t>2028-3-23</t>
+  </si>
+  <si>
+    <t>MA2813</t>
+  </si>
+  <si>
+    <t>2028-3-30</t>
+  </si>
+  <si>
+    <t>AB2814</t>
+  </si>
+  <si>
+    <t>2028-4-6</t>
+  </si>
+  <si>
+    <t>AB2815</t>
+  </si>
+  <si>
+    <t>2028-4-13</t>
+  </si>
+  <si>
+    <t>AB2816</t>
+  </si>
+  <si>
+    <t>2028-4-20</t>
+  </si>
+  <si>
+    <t>AB2817</t>
+  </si>
+  <si>
+    <t>2028-4-27</t>
+  </si>
+  <si>
+    <t>MY2818</t>
+  </si>
+  <si>
+    <t>2028-5-4</t>
+  </si>
+  <si>
+    <t>MY2819</t>
+  </si>
+  <si>
+    <t>2028-5-11</t>
+  </si>
+  <si>
+    <t>MY2820</t>
+  </si>
+  <si>
+    <t>2028-5-18</t>
+  </si>
+  <si>
+    <t>MY2821</t>
+  </si>
+  <si>
+    <t>2028-5-25</t>
+  </si>
+  <si>
+    <t>JU2822</t>
+  </si>
+  <si>
+    <t>2028-6-1</t>
+  </si>
+  <si>
+    <t>JU2823</t>
+  </si>
+  <si>
+    <t>2028-6-8</t>
+  </si>
+  <si>
+    <t>JU2824</t>
+  </si>
+  <si>
+    <t>2028-6-15</t>
+  </si>
+  <si>
+    <t>JU2825</t>
+  </si>
+  <si>
+    <t>2028-6-22</t>
+  </si>
+  <si>
+    <t>JU2826</t>
+  </si>
+  <si>
+    <t>2028-6-29</t>
+  </si>
+  <si>
+    <t>JL2827</t>
+  </si>
+  <si>
+    <t>2028-7-6</t>
+  </si>
+  <si>
+    <t>JL2828</t>
+  </si>
+  <si>
+    <t>2028-7-13</t>
+  </si>
+  <si>
+    <t>JL2829</t>
+  </si>
+  <si>
+    <t>2028-7-20</t>
+  </si>
+  <si>
+    <t>JL2830</t>
+  </si>
+  <si>
+    <t>2028-7-27</t>
+  </si>
+  <si>
+    <t>AG2831</t>
+  </si>
+  <si>
+    <t>2028-8-3</t>
+  </si>
+  <si>
+    <t>AG2832</t>
+  </si>
+  <si>
+    <t>2028-8-10</t>
+  </si>
+  <si>
+    <t>AG2833</t>
+  </si>
+  <si>
+    <t>2028-8-17</t>
+  </si>
+  <si>
+    <t>AG2834</t>
+  </si>
+  <si>
+    <t>2028-8-24</t>
+  </si>
+  <si>
+    <t>AG2835</t>
+  </si>
+  <si>
+    <t>2028-8-31</t>
+  </si>
+  <si>
+    <t>SE2836</t>
+  </si>
+  <si>
+    <t>2028-9-7</t>
+  </si>
+  <si>
+    <t>SE2837</t>
+  </si>
+  <si>
+    <t>2028-9-14</t>
+  </si>
+  <si>
+    <t>SE2838</t>
+  </si>
+  <si>
+    <t>2028-9-21</t>
+  </si>
+  <si>
+    <t>SE2839</t>
+  </si>
+  <si>
+    <t>2028-9-28</t>
+  </si>
+  <si>
+    <t>OC2840</t>
+  </si>
+  <si>
+    <t>2028-10-5</t>
+  </si>
+  <si>
+    <t>OC2841</t>
+  </si>
+  <si>
+    <t>2028-10-12</t>
+  </si>
+  <si>
+    <t>OC2842</t>
+  </si>
+  <si>
+    <t>2028-10-19</t>
+  </si>
+  <si>
+    <t>OC2843</t>
+  </si>
+  <si>
+    <t>2028-10-26</t>
+  </si>
+  <si>
+    <t>NO2844</t>
+  </si>
+  <si>
+    <t>2028-11-2</t>
+  </si>
+  <si>
+    <t>NO2845</t>
+  </si>
+  <si>
+    <t>2028-11-9</t>
+  </si>
+  <si>
+    <t>NO2846</t>
+  </si>
+  <si>
+    <t>2028-11-16</t>
+  </si>
+  <si>
+    <t>NO2847</t>
+  </si>
+  <si>
+    <t>2028-11-23</t>
+  </si>
+  <si>
+    <t>NO2848</t>
+  </si>
+  <si>
+    <t>2028-11-30</t>
+  </si>
+  <si>
+    <t>DI2849</t>
+  </si>
+  <si>
+    <t>2028-12-7</t>
+  </si>
+  <si>
+    <t>DI2850</t>
+  </si>
+  <si>
+    <t>2028-12-14</t>
+  </si>
+  <si>
+    <t>DI2851</t>
+  </si>
+  <si>
+    <t>2028-12-21</t>
+  </si>
+  <si>
+    <t>DI2852</t>
+  </si>
+  <si>
+    <t>2028-12-28</t>
+  </si>
+  <si>
+    <t>EN2901</t>
+  </si>
+  <si>
+    <t>2029-1-4</t>
+  </si>
+  <si>
+    <t>EN2902</t>
+  </si>
+  <si>
+    <t>2029-1-11</t>
+  </si>
+  <si>
+    <t>EN2903</t>
+  </si>
+  <si>
+    <t>2029-1-18</t>
+  </si>
+  <si>
+    <t>EN2904</t>
+  </si>
+  <si>
+    <t>2029-1-25</t>
+  </si>
+  <si>
+    <t>FE2905</t>
+  </si>
+  <si>
+    <t>2029-2-1</t>
+  </si>
+  <si>
+    <t>FE2906</t>
+  </si>
+  <si>
+    <t>2029-2-8</t>
+  </si>
+  <si>
+    <t>FE2907</t>
+  </si>
+  <si>
+    <t>2029-2-15</t>
+  </si>
+  <si>
+    <t>FE2908</t>
+  </si>
+  <si>
+    <t>2029-2-22</t>
+  </si>
+  <si>
+    <t>MA2909</t>
+  </si>
+  <si>
+    <t>2029-3-1</t>
+  </si>
+  <si>
+    <t>MA2910</t>
+  </si>
+  <si>
+    <t>2029-3-8</t>
+  </si>
+  <si>
+    <t>MA2911</t>
+  </si>
+  <si>
+    <t>2029-3-15</t>
+  </si>
+  <si>
+    <t>MA2912</t>
+  </si>
+  <si>
+    <t>2029-3-22</t>
+  </si>
+  <si>
+    <t>MA2913</t>
+  </si>
+  <si>
+    <t>2029-3-29</t>
+  </si>
+  <si>
+    <t>AB2914</t>
+  </si>
+  <si>
+    <t>2029-4-5</t>
+  </si>
+  <si>
+    <t>AB2915</t>
+  </si>
+  <si>
+    <t>2029-4-12</t>
+  </si>
+  <si>
+    <t>AB2916</t>
+  </si>
+  <si>
+    <t>2029-4-19</t>
+  </si>
+  <si>
+    <t>AB2917</t>
+  </si>
+  <si>
+    <t>2029-4-26</t>
+  </si>
+  <si>
+    <t>MY2918</t>
+  </si>
+  <si>
+    <t>2029-5-3</t>
+  </si>
+  <si>
+    <t>MY2919</t>
+  </si>
+  <si>
+    <t>2029-5-10</t>
+  </si>
+  <si>
+    <t>MY2920</t>
+  </si>
+  <si>
+    <t>2029-5-17</t>
+  </si>
+  <si>
+    <t>MY2921</t>
+  </si>
+  <si>
+    <t>2029-5-24</t>
+  </si>
+  <si>
+    <t>MY2922</t>
+  </si>
+  <si>
+    <t>2029-5-31</t>
+  </si>
+  <si>
+    <t>JU2923</t>
+  </si>
+  <si>
+    <t>2029-6-7</t>
+  </si>
+  <si>
+    <t>JU2924</t>
+  </si>
+  <si>
+    <t>2029-6-14</t>
+  </si>
+  <si>
+    <t>JU2925</t>
+  </si>
+  <si>
+    <t>2029-6-21</t>
+  </si>
+  <si>
+    <t>JU2926</t>
+  </si>
+  <si>
+    <t>2029-6-28</t>
+  </si>
+  <si>
+    <t>JL2927</t>
+  </si>
+  <si>
+    <t>2029-7-5</t>
+  </si>
+  <si>
+    <t>JL2928</t>
+  </si>
+  <si>
+    <t>2029-7-12</t>
+  </si>
+  <si>
+    <t>JL2929</t>
+  </si>
+  <si>
+    <t>2029-7-19</t>
+  </si>
+  <si>
+    <t>JL2930</t>
+  </si>
+  <si>
+    <t>2029-7-26</t>
+  </si>
+  <si>
+    <t>AG2931</t>
+  </si>
+  <si>
+    <t>2029-8-2</t>
+  </si>
+  <si>
+    <t>AG2932</t>
+  </si>
+  <si>
+    <t>2029-8-9</t>
+  </si>
+  <si>
+    <t>AG2933</t>
+  </si>
+  <si>
+    <t>2029-8-16</t>
+  </si>
+  <si>
+    <t>AG2934</t>
+  </si>
+  <si>
+    <t>2029-8-23</t>
+  </si>
+  <si>
+    <t>AG2935</t>
+  </si>
+  <si>
+    <t>2029-8-30</t>
+  </si>
+  <si>
+    <t>SE2936</t>
+  </si>
+  <si>
+    <t>2029-9-6</t>
+  </si>
+  <si>
+    <t>SE2937</t>
+  </si>
+  <si>
+    <t>2029-9-13</t>
+  </si>
+  <si>
+    <t>SE2938</t>
+  </si>
+  <si>
+    <t>2029-9-20</t>
+  </si>
+  <si>
+    <t>SE2939</t>
+  </si>
+  <si>
+    <t>2029-9-27</t>
+  </si>
+  <si>
+    <t>OC2940</t>
+  </si>
+  <si>
+    <t>2029-10-4</t>
+  </si>
+  <si>
+    <t>OC2941</t>
+  </si>
+  <si>
+    <t>2029-10-11</t>
+  </si>
+  <si>
+    <t>OC2942</t>
+  </si>
+  <si>
+    <t>2029-10-18</t>
+  </si>
+  <si>
+    <t>OC2943</t>
+  </si>
+  <si>
+    <t>2029-10-25</t>
+  </si>
+  <si>
+    <t>NO2944</t>
+  </si>
+  <si>
+    <t>2029-11-1</t>
+  </si>
+  <si>
+    <t>NO2945</t>
+  </si>
+  <si>
+    <t>2029-11-8</t>
+  </si>
+  <si>
+    <t>NO2946</t>
+  </si>
+  <si>
+    <t>2029-11-15</t>
+  </si>
+  <si>
+    <t>NO2947</t>
+  </si>
+  <si>
+    <t>2029-11-22</t>
+  </si>
+  <si>
+    <t>NO2948</t>
+  </si>
+  <si>
+    <t>2029-11-29</t>
+  </si>
+  <si>
+    <t>DI2949</t>
+  </si>
+  <si>
+    <t>2029-12-6</t>
+  </si>
+  <si>
+    <t>DI2950</t>
+  </si>
+  <si>
+    <t>2029-12-13</t>
+  </si>
+  <si>
+    <t>DI2951</t>
+  </si>
+  <si>
+    <t>2029-12-20</t>
+  </si>
+  <si>
+    <t>DI2952</t>
+  </si>
+  <si>
+    <t>2029-12-27</t>
   </si>
 </sst>
 </file>
@@ -4152,14 +5088,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4188,7 +5124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
@@ -4199,41 +5135,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4300,6 +5207,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
       </font>
@@ -4323,8 +5270,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="23"/>
-      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="wholeTable" dxfId="24"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4339,23 +5286,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="temporadas" displayName="temporadas" ref="A1:K424">
-  <autoFilter ref="A1:K424" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="temporadas" displayName="temporadas" ref="A1:K580">
+  <autoFilter ref="A1:K580" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K302">
     <sortCondition ref="J1:J302"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="cosecha" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="fiesta" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="cosecha" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="fiesta" dataDxfId="16" totalsRowDxfId="15"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="año"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="fecha_pico" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="fecha_calendario" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="cod_temporada" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="fecha_pico" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="fecha_calendario" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="cod_temporada" dataDxfId="10" totalsRowDxfId="9"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="tipo"/>
-    <tableColumn id="8" xr3:uid="{6ACCE494-4F07-4643-AFCD-95DDBCC2C9EE}" name="mes_siembra" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{5128351C-7F2E-4A3D-B8E6-D727EA4B9857}" name="ano_fiesta" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{8E9619AF-5A97-48DD-9DAC-3EC13FF072F8}" name="orden" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{6957B8E3-192A-46E9-A737-99B24B3FE74B}" name="Columna1" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="8" xr3:uid="{6ACCE494-4F07-4643-AFCD-95DDBCC2C9EE}" name="mes_siembra" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{5128351C-7F2E-4A3D-B8E6-D727EA4B9857}" name="ano_fiesta" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{8E9619AF-5A97-48DD-9DAC-3EC13FF072F8}" name="orden" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{6957B8E3-192A-46E9-A737-99B24B3FE74B}" name="Columna1" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="1">
       <calculatedColumnFormula>DATE(YEAR(temporadas[[#This Row],[fecha_pico]]),MONTH(temporadas[[#This Row],[fecha_pico]]),DAY(temporadas[[#This Row],[fecha_pico]]))</calculatedColumnFormula>
       <totalsRowFormula>+K320+7</totalsRowFormula>
     </tableColumn>
@@ -4365,9 +5312,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4405,9 +5352,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4440,9 +5387,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4475,9 +5439,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4652,7 +5633,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N585"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" style="1" bestFit="1" customWidth="1"/>
@@ -18752,7 +19733,7 @@
         <v>385</v>
       </c>
       <c r="K386" s="7">
-        <f t="shared" ref="K386:K424" si="1">+K385+7</f>
+        <f t="shared" ref="K386:K449" si="1">+K385+7</f>
         <v>46121</v>
       </c>
     </row>
@@ -20125,33 +21106,5652 @@
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K425" s="7"/>
+      <c r="A425" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B425" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C425" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E425" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F425" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G425" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H425" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I425">
+        <v>2027</v>
+      </c>
+      <c r="J425" s="3">
+        <v>424</v>
+      </c>
+      <c r="K425" s="7">
+        <f t="shared" si="1"/>
+        <v>46394</v>
+      </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K426" s="7"/>
+      <c r="A426" s="10" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B426" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C426" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E426" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F426" s="10" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G426" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H426" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I426">
+        <v>2027</v>
+      </c>
+      <c r="J426" s="3">
+        <v>425</v>
+      </c>
+      <c r="K426" s="7">
+        <f t="shared" si="1"/>
+        <v>46401</v>
+      </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K427" s="7"/>
+      <c r="A427" s="10" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B427" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C427" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E427" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F427" s="10" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G427" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H427" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I427">
+        <v>2027</v>
+      </c>
+      <c r="J427" s="3">
+        <v>426</v>
+      </c>
+      <c r="K427" s="7">
+        <f t="shared" si="1"/>
+        <v>46408</v>
+      </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K428" s="7"/>
+      <c r="A428" s="10" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B428" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C428" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E428" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F428" s="10" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G428" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H428" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I428">
+        <v>2027</v>
+      </c>
+      <c r="J428" s="3">
+        <v>427</v>
+      </c>
+      <c r="K428" s="7">
+        <f t="shared" si="1"/>
+        <v>46415</v>
+      </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K429" s="7"/>
+      <c r="A429" s="10" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B429" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C429" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E429" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F429" s="10" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G429" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H429" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I429">
+        <v>2027</v>
+      </c>
+      <c r="J429" s="3">
+        <v>428</v>
+      </c>
+      <c r="K429" s="7">
+        <f t="shared" si="1"/>
+        <v>46422</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A430" s="10" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B430" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C430" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E430" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F430" s="10" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G430" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H430" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I430">
+        <v>2027</v>
+      </c>
+      <c r="J430" s="3">
+        <v>429</v>
+      </c>
+      <c r="K430" s="7">
+        <f t="shared" si="1"/>
+        <v>46429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A431" s="10" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B431" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C431" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E431" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F431" s="10" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G431" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H431" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I431">
+        <v>2027</v>
+      </c>
+      <c r="J431" s="3">
+        <v>430</v>
+      </c>
+      <c r="K431" s="7">
+        <f t="shared" si="1"/>
+        <v>46436</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A432" s="10" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B432" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C432" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E432" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F432" s="10" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G432" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H432" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I432">
+        <v>2027</v>
+      </c>
+      <c r="J432" s="3">
+        <v>431</v>
+      </c>
+      <c r="K432" s="7">
+        <f t="shared" si="1"/>
+        <v>46443</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A433" s="10" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B433" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C433" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E433" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F433" s="10" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G433" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H433" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I433">
+        <v>2027</v>
+      </c>
+      <c r="J433" s="3">
+        <v>432</v>
+      </c>
+      <c r="K433" s="7">
+        <f t="shared" si="1"/>
+        <v>46450</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A434" s="10" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B434" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C434" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E434" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F434" s="10" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G434" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H434" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I434">
+        <v>2027</v>
+      </c>
+      <c r="J434" s="3">
+        <v>433</v>
+      </c>
+      <c r="K434" s="7">
+        <f t="shared" si="1"/>
+        <v>46457</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A435" s="10" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B435" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C435" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E435" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F435" s="10" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G435" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H435" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I435">
+        <v>2027</v>
+      </c>
+      <c r="J435" s="3">
+        <v>434</v>
+      </c>
+      <c r="K435" s="7">
+        <f t="shared" si="1"/>
+        <v>46464</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A436" s="10" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B436" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C436" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E436" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F436" s="10" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G436" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H436" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I436">
+        <v>2027</v>
+      </c>
+      <c r="J436" s="3">
+        <v>435</v>
+      </c>
+      <c r="K436" s="7">
+        <f t="shared" si="1"/>
+        <v>46471</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A437" s="10" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B437" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C437" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E437" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F437" s="10" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G437" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H437" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I437">
+        <v>2027</v>
+      </c>
+      <c r="J437" s="3">
+        <v>436</v>
+      </c>
+      <c r="K437" s="7">
+        <f t="shared" si="1"/>
+        <v>46478</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A438" s="10" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B438" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C438" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E438" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F438" s="10" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G438" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H438" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I438">
+        <v>2027</v>
+      </c>
+      <c r="J438" s="3">
+        <v>437</v>
+      </c>
+      <c r="K438" s="7">
+        <f t="shared" si="1"/>
+        <v>46485</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A439" s="10" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B439" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C439" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E439" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F439" s="10" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G439" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H439" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I439">
+        <v>2027</v>
+      </c>
+      <c r="J439" s="3">
+        <v>438</v>
+      </c>
+      <c r="K439" s="7">
+        <f t="shared" si="1"/>
+        <v>46492</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A440" s="10" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B440" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C440" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E440" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F440" s="10" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G440" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H440" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I440">
+        <v>2027</v>
+      </c>
+      <c r="J440" s="3">
+        <v>439</v>
+      </c>
+      <c r="K440" s="7">
+        <f t="shared" si="1"/>
+        <v>46499</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A441" s="10" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B441" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C441" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D441" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E441" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F441" s="10" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G441" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H441" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I441">
+        <v>2027</v>
+      </c>
+      <c r="J441" s="3">
+        <v>440</v>
+      </c>
+      <c r="K441" s="7">
+        <f t="shared" si="1"/>
+        <v>46506</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A442" s="10" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B442" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C442" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D442" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E442" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F442" s="10" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G442" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H442" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I442">
+        <v>2027</v>
+      </c>
+      <c r="J442" s="3">
+        <v>441</v>
+      </c>
+      <c r="K442" s="7">
+        <f t="shared" si="1"/>
+        <v>46513</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A443" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B443" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C443" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D443" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E443" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F443" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G443" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H443" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I443">
+        <v>2027</v>
+      </c>
+      <c r="J443" s="3">
+        <v>442</v>
+      </c>
+      <c r="K443" s="7">
+        <f t="shared" si="1"/>
+        <v>46520</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A444" s="10" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B444" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C444" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E444" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F444" s="10" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G444" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H444" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I444">
+        <v>2027</v>
+      </c>
+      <c r="J444" s="3">
+        <v>443</v>
+      </c>
+      <c r="K444" s="7">
+        <f t="shared" si="1"/>
+        <v>46527</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A445" s="10" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B445" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C445" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D445" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E445" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F445" s="10" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G445" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H445" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I445">
+        <v>2027</v>
+      </c>
+      <c r="J445" s="3">
+        <v>444</v>
+      </c>
+      <c r="K445" s="7">
+        <f t="shared" si="1"/>
+        <v>46534</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A446" s="10" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B446" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C446" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D446" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E446" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F446" s="10" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G446" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H446" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I446">
+        <v>2027</v>
+      </c>
+      <c r="J446" s="3">
+        <v>445</v>
+      </c>
+      <c r="K446" s="7">
+        <f t="shared" si="1"/>
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A447" s="10" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B447" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C447" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D447" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E447" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F447" s="10" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G447" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H447" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I447">
+        <v>2027</v>
+      </c>
+      <c r="J447" s="3">
+        <v>446</v>
+      </c>
+      <c r="K447" s="7">
+        <f t="shared" si="1"/>
+        <v>46548</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A448" s="10" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B448" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C448" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D448" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E448" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F448" s="10" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G448" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H448" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I448">
+        <v>2027</v>
+      </c>
+      <c r="J448" s="3">
+        <v>447</v>
+      </c>
+      <c r="K448" s="7">
+        <f t="shared" si="1"/>
+        <v>46555</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A449" s="10" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B449" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C449" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D449" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E449" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F449" s="10" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G449" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H449" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I449">
+        <v>2027</v>
+      </c>
+      <c r="J449" s="3">
+        <v>448</v>
+      </c>
+      <c r="K449" s="7">
+        <f t="shared" si="1"/>
+        <v>46562</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A450" s="10" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B450" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C450" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D450" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E450" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F450" s="10" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G450" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H450" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I450">
+        <v>2028</v>
+      </c>
+      <c r="J450" s="3">
+        <v>449</v>
+      </c>
+      <c r="K450" s="7">
+        <f t="shared" ref="K450:K513" si="2">+K449+7</f>
+        <v>46569</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A451" s="10" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B451" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C451" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D451" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E451" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F451" s="10" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G451" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H451" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I451">
+        <v>2028</v>
+      </c>
+      <c r="J451" s="3">
+        <v>450</v>
+      </c>
+      <c r="K451" s="7">
+        <f t="shared" si="2"/>
+        <v>46576</v>
+      </c>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A452" s="10" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B452" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C452" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D452" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E452" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F452" s="10" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G452" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H452" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I452">
+        <v>2028</v>
+      </c>
+      <c r="J452" s="3">
+        <v>451</v>
+      </c>
+      <c r="K452" s="7">
+        <f t="shared" si="2"/>
+        <v>46583</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A453" s="10" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B453" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C453" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E453" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F453" s="10" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G453" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H453" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I453">
+        <v>2028</v>
+      </c>
+      <c r="J453" s="3">
+        <v>452</v>
+      </c>
+      <c r="K453" s="7">
+        <f t="shared" si="2"/>
+        <v>46590</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A454" s="10" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B454" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C454" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D454" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E454" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F454" s="10" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G454" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H454" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I454">
+        <v>2028</v>
+      </c>
+      <c r="J454" s="3">
+        <v>453</v>
+      </c>
+      <c r="K454" s="7">
+        <f t="shared" si="2"/>
+        <v>46597</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A455" s="10" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B455" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C455" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D455" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E455" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F455" s="10" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G455" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H455" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I455">
+        <v>2028</v>
+      </c>
+      <c r="J455" s="3">
+        <v>454</v>
+      </c>
+      <c r="K455" s="7">
+        <f t="shared" si="2"/>
+        <v>46604</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A456" s="10" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B456" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C456" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D456" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E456" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F456" s="10" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G456" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H456" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I456">
+        <v>2028</v>
+      </c>
+      <c r="J456" s="3">
+        <v>455</v>
+      </c>
+      <c r="K456" s="7">
+        <f t="shared" si="2"/>
+        <v>46611</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A457" s="10" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B457" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C457" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D457" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E457" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F457" s="10" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G457" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H457" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I457">
+        <v>2028</v>
+      </c>
+      <c r="J457" s="3">
+        <v>456</v>
+      </c>
+      <c r="K457" s="7">
+        <f t="shared" si="2"/>
+        <v>46618</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A458" s="10" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B458" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C458" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D458" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E458" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F458" s="10" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G458" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H458" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I458">
+        <v>2028</v>
+      </c>
+      <c r="J458" s="3">
+        <v>457</v>
+      </c>
+      <c r="K458" s="7">
+        <f t="shared" si="2"/>
+        <v>46625</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A459" s="10" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B459" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C459" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D459" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E459" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F459" s="10" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G459" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H459" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I459">
+        <v>2028</v>
+      </c>
+      <c r="J459" s="3">
+        <v>458</v>
+      </c>
+      <c r="K459" s="7">
+        <f t="shared" si="2"/>
+        <v>46632</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A460" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B460" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C460" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D460" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E460" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F460" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G460" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H460" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I460">
+        <v>2028</v>
+      </c>
+      <c r="J460" s="3">
+        <v>459</v>
+      </c>
+      <c r="K460" s="7">
+        <f t="shared" si="2"/>
+        <v>46639</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A461" s="10" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B461" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C461" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D461" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E461" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F461" s="10" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G461" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H461" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I461">
+        <v>2028</v>
+      </c>
+      <c r="J461" s="3">
+        <v>460</v>
+      </c>
+      <c r="K461" s="7">
+        <f t="shared" si="2"/>
+        <v>46646</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A462" s="10" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B462" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C462" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D462" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E462" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F462" s="10" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G462" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H462" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I462">
+        <v>2028</v>
+      </c>
+      <c r="J462" s="3">
+        <v>461</v>
+      </c>
+      <c r="K462" s="7">
+        <f t="shared" si="2"/>
+        <v>46653</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A463" s="10" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B463" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C463" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D463" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E463" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F463" s="10" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G463" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H463" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I463">
+        <v>2028</v>
+      </c>
+      <c r="J463" s="3">
+        <v>462</v>
+      </c>
+      <c r="K463" s="7">
+        <f t="shared" si="2"/>
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A464" s="10" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B464" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C464" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D464" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E464" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F464" s="10" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G464" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H464" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I464">
+        <v>2028</v>
+      </c>
+      <c r="J464" s="3">
+        <v>463</v>
+      </c>
+      <c r="K464" s="7">
+        <f t="shared" si="2"/>
+        <v>46667</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A465" s="10" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B465" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C465" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E465" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F465" s="10" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G465" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H465" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I465">
+        <v>2028</v>
+      </c>
+      <c r="J465" s="3">
+        <v>464</v>
+      </c>
+      <c r="K465" s="7">
+        <f t="shared" si="2"/>
+        <v>46674</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A466" s="10" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B466" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C466" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D466" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E466" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F466" s="10" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G466" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H466" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I466">
+        <v>2028</v>
+      </c>
+      <c r="J466" s="3">
+        <v>465</v>
+      </c>
+      <c r="K466" s="7">
+        <f t="shared" si="2"/>
+        <v>46681</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A467" s="10" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B467" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C467" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D467" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E467" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F467" s="10" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G467" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H467" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I467">
+        <v>2028</v>
+      </c>
+      <c r="J467" s="3">
+        <v>466</v>
+      </c>
+      <c r="K467" s="7">
+        <f t="shared" si="2"/>
+        <v>46688</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A468" s="10" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B468" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C468" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D468" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E468" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F468" s="10" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G468" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H468" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I468">
+        <v>2028</v>
+      </c>
+      <c r="J468" s="3">
+        <v>467</v>
+      </c>
+      <c r="K468" s="7">
+        <f t="shared" si="2"/>
+        <v>46695</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A469" s="10" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B469" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C469" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D469" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E469" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F469" s="10" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G469" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H469" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I469">
+        <v>2028</v>
+      </c>
+      <c r="J469" s="3">
+        <v>468</v>
+      </c>
+      <c r="K469" s="7">
+        <f t="shared" si="2"/>
+        <v>46702</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A470" s="10" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B470" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C470" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D470" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E470" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F470" s="10" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G470" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H470" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I470">
+        <v>2028</v>
+      </c>
+      <c r="J470" s="3">
+        <v>469</v>
+      </c>
+      <c r="K470" s="7">
+        <f t="shared" si="2"/>
+        <v>46709</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A471" s="10" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B471" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C471" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D471" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E471" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F471" s="10" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G471" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H471" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I471">
+        <v>2028</v>
+      </c>
+      <c r="J471" s="3">
+        <v>470</v>
+      </c>
+      <c r="K471" s="7">
+        <f t="shared" si="2"/>
+        <v>46716</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A472" s="10" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B472" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C472" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E472" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F472" s="10" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G472" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H472" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I472">
+        <v>2028</v>
+      </c>
+      <c r="J472" s="3">
+        <v>471</v>
+      </c>
+      <c r="K472" s="7">
+        <f t="shared" si="2"/>
+        <v>46723</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A473" s="10" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B473" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C473" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D473" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E473" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F473" s="10" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G473" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H473" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I473">
+        <v>2028</v>
+      </c>
+      <c r="J473" s="3">
+        <v>472</v>
+      </c>
+      <c r="K473" s="7">
+        <f t="shared" si="2"/>
+        <v>46730</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A474" s="10" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B474" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C474" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D474" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E474" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F474" s="10" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G474" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H474" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I474">
+        <v>2028</v>
+      </c>
+      <c r="J474" s="3">
+        <v>473</v>
+      </c>
+      <c r="K474" s="7">
+        <f t="shared" si="2"/>
+        <v>46737</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A475" s="10" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B475" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C475" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D475" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E475" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F475" s="10" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G475" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H475" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I475">
+        <v>2028</v>
+      </c>
+      <c r="J475" s="3">
+        <v>474</v>
+      </c>
+      <c r="K475" s="7">
+        <f t="shared" si="2"/>
+        <v>46744</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A476" s="10" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B476" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C476" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D476" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E476" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F476" s="10" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G476" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H476" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I476">
+        <v>2028</v>
+      </c>
+      <c r="J476" s="3">
+        <v>475</v>
+      </c>
+      <c r="K476" s="7">
+        <f t="shared" si="2"/>
+        <v>46751</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A477" s="10" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B477" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C477" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D477" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E477" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F477" s="10" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G477" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H477" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I477">
+        <v>2028</v>
+      </c>
+      <c r="J477" s="3">
+        <v>476</v>
+      </c>
+      <c r="K477" s="7">
+        <f t="shared" si="2"/>
+        <v>46758</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A478" s="10" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B478" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C478" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E478" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F478" s="10" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G478" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H478" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I478">
+        <v>2028</v>
+      </c>
+      <c r="J478" s="3">
+        <v>477</v>
+      </c>
+      <c r="K478" s="7">
+        <f t="shared" si="2"/>
+        <v>46765</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A479" s="10" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B479" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C479" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D479" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E479" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F479" s="10" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G479" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H479" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I479">
+        <v>2028</v>
+      </c>
+      <c r="J479" s="3">
+        <v>478</v>
+      </c>
+      <c r="K479" s="7">
+        <f t="shared" si="2"/>
+        <v>46772</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A480" s="10" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B480" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C480" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D480" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E480" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="F480" s="10" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G480" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H480" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I480">
+        <v>2028</v>
+      </c>
+      <c r="J480" s="3">
+        <v>479</v>
+      </c>
+      <c r="K480" s="7">
+        <f t="shared" si="2"/>
+        <v>46779</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A481" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B481" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C481" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E481" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F481" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G481" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H481" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I481">
+        <v>2028</v>
+      </c>
+      <c r="J481" s="3">
+        <v>480</v>
+      </c>
+      <c r="K481" s="7">
+        <f t="shared" si="2"/>
+        <v>46786</v>
+      </c>
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A482" s="10" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B482" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C482" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F482" s="10" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G482" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H482" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I482">
+        <v>2028</v>
+      </c>
+      <c r="J482" s="3">
+        <v>481</v>
+      </c>
+      <c r="K482" s="7">
+        <f t="shared" si="2"/>
+        <v>46793</v>
+      </c>
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A483" s="10" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B483" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C483" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D483" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E483" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F483" s="10" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G483" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H483" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I483">
+        <v>2028</v>
+      </c>
+      <c r="J483" s="3">
+        <v>482</v>
+      </c>
+      <c r="K483" s="7">
+        <f t="shared" si="2"/>
+        <v>46800</v>
+      </c>
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A484" s="10" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B484" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C484" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E484" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F484" s="10" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G484" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H484" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I484">
+        <v>2028</v>
+      </c>
+      <c r="J484" s="3">
+        <v>483</v>
+      </c>
+      <c r="K484" s="7">
+        <f t="shared" si="2"/>
+        <v>46807</v>
+      </c>
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A485" s="10" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B485" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C485" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F485" s="10" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G485" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H485" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I485">
+        <v>2028</v>
+      </c>
+      <c r="J485" s="3">
+        <v>484</v>
+      </c>
+      <c r="K485" s="7">
+        <f t="shared" si="2"/>
+        <v>46814</v>
+      </c>
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A486" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B486" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C486" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D486" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F486" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G486" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H486" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I486">
+        <v>2028</v>
+      </c>
+      <c r="J486" s="3">
+        <v>485</v>
+      </c>
+      <c r="K486" s="7">
+        <f t="shared" si="2"/>
+        <v>46821</v>
+      </c>
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A487" s="10" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B487" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C487" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D487" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F487" s="10" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G487" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H487" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I487">
+        <v>2028</v>
+      </c>
+      <c r="J487" s="3">
+        <v>486</v>
+      </c>
+      <c r="K487" s="7">
+        <f t="shared" si="2"/>
+        <v>46828</v>
+      </c>
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A488" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B488" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C488" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F488" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G488" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H488" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I488">
+        <v>2028</v>
+      </c>
+      <c r="J488" s="3">
+        <v>487</v>
+      </c>
+      <c r="K488" s="7">
+        <f t="shared" si="2"/>
+        <v>46835</v>
+      </c>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A489" s="10" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B489" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C489" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D489" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E489" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F489" s="10" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G489" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H489" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I489">
+        <v>2028</v>
+      </c>
+      <c r="J489" s="3">
+        <v>488</v>
+      </c>
+      <c r="K489" s="7">
+        <f t="shared" si="2"/>
+        <v>46842</v>
+      </c>
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A490" s="10" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B490" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C490" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D490" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F490" s="10" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G490" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H490" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I490">
+        <v>2028</v>
+      </c>
+      <c r="J490" s="3">
+        <v>489</v>
+      </c>
+      <c r="K490" s="7">
+        <f t="shared" si="2"/>
+        <v>46849</v>
+      </c>
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A491" s="10" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B491" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C491" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D491" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E491" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F491" s="10" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G491" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H491" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I491">
+        <v>2028</v>
+      </c>
+      <c r="J491" s="3">
+        <v>490</v>
+      </c>
+      <c r="K491" s="7">
+        <f t="shared" si="2"/>
+        <v>46856</v>
+      </c>
+    </row>
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A492" s="10" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B492" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C492" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E492" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F492" s="10" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G492" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H492" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I492">
+        <v>2028</v>
+      </c>
+      <c r="J492" s="3">
+        <v>491</v>
+      </c>
+      <c r="K492" s="7">
+        <f t="shared" si="2"/>
+        <v>46863</v>
+      </c>
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A493" s="10" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B493" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C493" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D493" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E493" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F493" s="10" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G493" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H493" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I493">
+        <v>2028</v>
+      </c>
+      <c r="J493" s="3">
+        <v>492</v>
+      </c>
+      <c r="K493" s="7">
+        <f t="shared" si="2"/>
+        <v>46870</v>
+      </c>
+    </row>
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A494" s="10" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B494" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C494" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E494" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F494" s="10" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G494" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H494" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I494">
+        <v>2028</v>
+      </c>
+      <c r="J494" s="3">
+        <v>493</v>
+      </c>
+      <c r="K494" s="7">
+        <f t="shared" si="2"/>
+        <v>46877</v>
+      </c>
+    </row>
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A495" s="10" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B495" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C495" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D495" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E495" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F495" s="10" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G495" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H495" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I495">
+        <v>2028</v>
+      </c>
+      <c r="J495" s="3">
+        <v>494</v>
+      </c>
+      <c r="K495" s="7">
+        <f t="shared" si="2"/>
+        <v>46884</v>
+      </c>
+    </row>
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A496" s="10" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B496" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C496" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D496" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F496" s="10" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G496" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H496" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I496">
+        <v>2028</v>
+      </c>
+      <c r="J496" s="3">
+        <v>495</v>
+      </c>
+      <c r="K496" s="7">
+        <f t="shared" si="2"/>
+        <v>46891</v>
+      </c>
+    </row>
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A497" s="10" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B497" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C497" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D497" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E497" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F497" s="10" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G497" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H497" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I497">
+        <v>2028</v>
+      </c>
+      <c r="J497" s="3">
+        <v>496</v>
+      </c>
+      <c r="K497" s="7">
+        <f t="shared" si="2"/>
+        <v>46898</v>
+      </c>
+    </row>
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A498" s="10" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B498" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C498" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E498" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F498" s="10" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G498" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H498" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I498">
+        <v>2028</v>
+      </c>
+      <c r="J498" s="3">
+        <v>497</v>
+      </c>
+      <c r="K498" s="7">
+        <f t="shared" si="2"/>
+        <v>46905</v>
+      </c>
+    </row>
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A499" s="10" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B499" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C499" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F499" s="10" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G499" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H499" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I499">
+        <v>2028</v>
+      </c>
+      <c r="J499" s="3">
+        <v>498</v>
+      </c>
+      <c r="K499" s="7">
+        <f t="shared" si="2"/>
+        <v>46912</v>
+      </c>
+    </row>
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A500" s="10" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B500" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C500" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E500" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F500" s="10" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G500" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H500" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I500">
+        <v>2028</v>
+      </c>
+      <c r="J500" s="3">
+        <v>499</v>
+      </c>
+      <c r="K500" s="7">
+        <f t="shared" si="2"/>
+        <v>46919</v>
+      </c>
+    </row>
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A501" s="10" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B501" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C501" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D501" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E501" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F501" s="10" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G501" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H501" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I501">
+        <v>2028</v>
+      </c>
+      <c r="J501" s="3">
+        <v>500</v>
+      </c>
+      <c r="K501" s="7">
+        <f t="shared" si="2"/>
+        <v>46926</v>
+      </c>
+    </row>
+    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A502" s="10" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B502" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C502" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E502" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F502" s="10" t="s">
+        <v>1442</v>
+      </c>
+      <c r="G502" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H502" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I502">
+        <v>2028</v>
+      </c>
+      <c r="J502" s="3">
+        <v>501</v>
+      </c>
+      <c r="K502" s="7">
+        <f t="shared" si="2"/>
+        <v>46933</v>
+      </c>
+    </row>
+    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A503" s="10" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B503" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C503" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D503" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E503" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F503" s="10" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G503" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H503" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I503">
+        <v>2029</v>
+      </c>
+      <c r="J503" s="3">
+        <v>502</v>
+      </c>
+      <c r="K503" s="7">
+        <f t="shared" si="2"/>
+        <v>46940</v>
+      </c>
+    </row>
+    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A504" s="10" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B504" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C504" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E504" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F504" s="10" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G504" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H504" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I504">
+        <v>2029</v>
+      </c>
+      <c r="J504" s="3">
+        <v>503</v>
+      </c>
+      <c r="K504" s="7">
+        <f t="shared" si="2"/>
+        <v>46947</v>
+      </c>
+    </row>
+    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A505" s="10" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B505" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C505" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E505" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F505" s="10" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G505" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H505" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I505">
+        <v>2029</v>
+      </c>
+      <c r="J505" s="3">
+        <v>504</v>
+      </c>
+      <c r="K505" s="7">
+        <f t="shared" si="2"/>
+        <v>46954</v>
+      </c>
+    </row>
+    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A506" s="10" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B506" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C506" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E506" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F506" s="10" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G506" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H506" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I506">
+        <v>2029</v>
+      </c>
+      <c r="J506" s="3">
+        <v>505</v>
+      </c>
+      <c r="K506" s="7">
+        <f t="shared" si="2"/>
+        <v>46961</v>
+      </c>
+    </row>
+    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A507" s="10" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B507" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C507" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D507" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E507" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F507" s="10" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G507" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H507" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I507">
+        <v>2029</v>
+      </c>
+      <c r="J507" s="3">
+        <v>506</v>
+      </c>
+      <c r="K507" s="7">
+        <f t="shared" si="2"/>
+        <v>46968</v>
+      </c>
+    </row>
+    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A508" s="10" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B508" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C508" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E508" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F508" s="10" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G508" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H508" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I508">
+        <v>2029</v>
+      </c>
+      <c r="J508" s="3">
+        <v>507</v>
+      </c>
+      <c r="K508" s="7">
+        <f t="shared" si="2"/>
+        <v>46975</v>
+      </c>
+    </row>
+    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A509" s="10" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B509" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C509" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D509" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E509" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F509" s="10" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G509" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H509" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I509">
+        <v>2029</v>
+      </c>
+      <c r="J509" s="3">
+        <v>508</v>
+      </c>
+      <c r="K509" s="7">
+        <f t="shared" si="2"/>
+        <v>46982</v>
+      </c>
+    </row>
+    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A510" s="10" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B510" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C510" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D510" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E510" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F510" s="10" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G510" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H510" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I510">
+        <v>2029</v>
+      </c>
+      <c r="J510" s="3">
+        <v>509</v>
+      </c>
+      <c r="K510" s="7">
+        <f t="shared" si="2"/>
+        <v>46989</v>
+      </c>
+    </row>
+    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A511" s="10" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B511" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C511" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E511" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F511" s="10" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G511" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H511" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I511">
+        <v>2029</v>
+      </c>
+      <c r="J511" s="3">
+        <v>510</v>
+      </c>
+      <c r="K511" s="7">
+        <f t="shared" si="2"/>
+        <v>46996</v>
+      </c>
+    </row>
+    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A512" s="10" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B512" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C512" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D512" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E512" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F512" s="10" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G512" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H512" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I512">
+        <v>2029</v>
+      </c>
+      <c r="J512" s="3">
+        <v>511</v>
+      </c>
+      <c r="K512" s="7">
+        <f t="shared" si="2"/>
+        <v>47003</v>
+      </c>
+    </row>
+    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A513" s="10" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B513" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C513" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D513" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E513" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F513" s="10" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G513" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H513" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I513">
+        <v>2029</v>
+      </c>
+      <c r="J513" s="3">
+        <v>512</v>
+      </c>
+      <c r="K513" s="7">
+        <f t="shared" si="2"/>
+        <v>47010</v>
+      </c>
+    </row>
+    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A514" s="10" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B514" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C514" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E514" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F514" s="10" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G514" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H514" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I514">
+        <v>2029</v>
+      </c>
+      <c r="J514" s="3">
+        <v>513</v>
+      </c>
+      <c r="K514" s="7">
+        <f t="shared" ref="K514:K577" si="3">+K513+7</f>
+        <v>47017</v>
+      </c>
+    </row>
+    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A515" s="10" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B515" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C515" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E515" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F515" s="10" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G515" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H515" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I515">
+        <v>2029</v>
+      </c>
+      <c r="J515" s="3">
+        <v>514</v>
+      </c>
+      <c r="K515" s="7">
+        <f t="shared" si="3"/>
+        <v>47024</v>
+      </c>
+    </row>
+    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A516" s="10" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B516" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C516" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E516" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F516" s="10" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G516" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H516" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I516">
+        <v>2029</v>
+      </c>
+      <c r="J516" s="3">
+        <v>515</v>
+      </c>
+      <c r="K516" s="7">
+        <f t="shared" si="3"/>
+        <v>47031</v>
+      </c>
+    </row>
+    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A517" s="10" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B517" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C517" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F517" s="10" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G517" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H517" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I517">
+        <v>2029</v>
+      </c>
+      <c r="J517" s="3">
+        <v>516</v>
+      </c>
+      <c r="K517" s="7">
+        <f t="shared" si="3"/>
+        <v>47038</v>
+      </c>
+    </row>
+    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A518" s="10" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B518" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C518" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E518" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F518" s="10" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G518" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H518" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I518">
+        <v>2029</v>
+      </c>
+      <c r="J518" s="3">
+        <v>517</v>
+      </c>
+      <c r="K518" s="7">
+        <f t="shared" si="3"/>
+        <v>47045</v>
+      </c>
+    </row>
+    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A519" s="10" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B519" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C519" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E519" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F519" s="10" t="s">
+        <v>1476</v>
+      </c>
+      <c r="G519" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H519" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I519">
+        <v>2029</v>
+      </c>
+      <c r="J519" s="3">
+        <v>518</v>
+      </c>
+      <c r="K519" s="7">
+        <f t="shared" si="3"/>
+        <v>47052</v>
+      </c>
+    </row>
+    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A520" s="10" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B520" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C520" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E520" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F520" s="10" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G520" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H520" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I520">
+        <v>2029</v>
+      </c>
+      <c r="J520" s="3">
+        <v>519</v>
+      </c>
+      <c r="K520" s="7">
+        <f t="shared" si="3"/>
+        <v>47059</v>
+      </c>
+    </row>
+    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A521" s="10" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B521" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C521" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D521" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E521" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F521" s="10" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G521" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H521" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I521">
+        <v>2029</v>
+      </c>
+      <c r="J521" s="3">
+        <v>520</v>
+      </c>
+      <c r="K521" s="7">
+        <f t="shared" si="3"/>
+        <v>47066</v>
+      </c>
+    </row>
+    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A522" s="10" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B522" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C522" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E522" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F522" s="10" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G522" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H522" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I522">
+        <v>2029</v>
+      </c>
+      <c r="J522" s="3">
+        <v>521</v>
+      </c>
+      <c r="K522" s="7">
+        <f t="shared" si="3"/>
+        <v>47073</v>
+      </c>
+    </row>
+    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A523" s="10" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B523" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C523" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E523" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F523" s="10" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G523" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H523" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I523">
+        <v>2029</v>
+      </c>
+      <c r="J523" s="3">
+        <v>522</v>
+      </c>
+      <c r="K523" s="7">
+        <f t="shared" si="3"/>
+        <v>47080</v>
+      </c>
+    </row>
+    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A524" s="10" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B524" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C524" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E524" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F524" s="10" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G524" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H524" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I524">
+        <v>2029</v>
+      </c>
+      <c r="J524" s="3">
+        <v>523</v>
+      </c>
+      <c r="K524" s="7">
+        <f t="shared" si="3"/>
+        <v>47087</v>
+      </c>
+    </row>
+    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A525" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B525" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C525" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E525" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F525" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G525" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H525" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I525">
+        <v>2029</v>
+      </c>
+      <c r="J525" s="3">
+        <v>524</v>
+      </c>
+      <c r="K525" s="7">
+        <f t="shared" si="3"/>
+        <v>47094</v>
+      </c>
+    </row>
+    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A526" s="10" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B526" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C526" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E526" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F526" s="10" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G526" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H526" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I526">
+        <v>2029</v>
+      </c>
+      <c r="J526" s="3">
+        <v>525</v>
+      </c>
+      <c r="K526" s="7">
+        <f t="shared" si="3"/>
+        <v>47101</v>
+      </c>
+    </row>
+    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A527" s="10" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B527" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C527" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E527" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F527" s="10" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G527" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H527" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I527">
+        <v>2029</v>
+      </c>
+      <c r="J527" s="3">
+        <v>526</v>
+      </c>
+      <c r="K527" s="7">
+        <f t="shared" si="3"/>
+        <v>47108</v>
+      </c>
+    </row>
+    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A528" s="10" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B528" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C528" s="3">
+        <v>2027</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E528" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F528" s="10" t="s">
+        <v>1494</v>
+      </c>
+      <c r="G528" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H528" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I528">
+        <v>2029</v>
+      </c>
+      <c r="J528" s="3">
+        <v>527</v>
+      </c>
+      <c r="K528" s="7">
+        <f t="shared" si="3"/>
+        <v>47115</v>
+      </c>
+    </row>
+    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A529" s="10" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B529" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C529" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E529" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F529" s="10" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G529" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H529" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I529">
+        <v>2029</v>
+      </c>
+      <c r="J529" s="3">
+        <v>528</v>
+      </c>
+      <c r="K529" s="7">
+        <f t="shared" si="3"/>
+        <v>47122</v>
+      </c>
+    </row>
+    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A530" s="10" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B530" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C530" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D530" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E530" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F530" s="10" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G530" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H530" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I530">
+        <v>2029</v>
+      </c>
+      <c r="J530" s="3">
+        <v>529</v>
+      </c>
+      <c r="K530" s="7">
+        <f t="shared" si="3"/>
+        <v>47129</v>
+      </c>
+    </row>
+    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A531" s="10" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B531" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C531" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D531" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E531" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F531" s="10" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G531" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H531" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I531">
+        <v>2029</v>
+      </c>
+      <c r="J531" s="3">
+        <v>530</v>
+      </c>
+      <c r="K531" s="7">
+        <f t="shared" si="3"/>
+        <v>47136</v>
+      </c>
+    </row>
+    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A532" s="10" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B532" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C532" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E532" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F532" s="10" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G532" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H532" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="I532">
+        <v>2029</v>
+      </c>
+      <c r="J532" s="3">
+        <v>531</v>
+      </c>
+      <c r="K532" s="7">
+        <f t="shared" si="3"/>
+        <v>47143</v>
+      </c>
+    </row>
+    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A533" s="10" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B533" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C533" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D533" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E533" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F533" s="10" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G533" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H533" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I533">
+        <v>2029</v>
+      </c>
+      <c r="J533" s="3">
+        <v>532</v>
+      </c>
+      <c r="K533" s="7">
+        <f t="shared" si="3"/>
+        <v>47150</v>
+      </c>
+    </row>
+    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A534" s="10" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B534" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C534" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D534" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E534" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F534" s="10" t="s">
+        <v>1506</v>
+      </c>
+      <c r="G534" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H534" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I534">
+        <v>2029</v>
+      </c>
+      <c r="J534" s="3">
+        <v>533</v>
+      </c>
+      <c r="K534" s="7">
+        <f t="shared" si="3"/>
+        <v>47157</v>
+      </c>
+    </row>
+    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A535" s="10" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B535" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C535" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E535" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F535" s="10" t="s">
+        <v>1508</v>
+      </c>
+      <c r="G535" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H535" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I535">
+        <v>2029</v>
+      </c>
+      <c r="J535" s="3">
+        <v>534</v>
+      </c>
+      <c r="K535" s="7">
+        <f t="shared" si="3"/>
+        <v>47164</v>
+      </c>
+    </row>
+    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A536" s="10" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B536" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="C536" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D536" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E536" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F536" s="10" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G536" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H536" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I536">
+        <v>2029</v>
+      </c>
+      <c r="J536" s="3">
+        <v>535</v>
+      </c>
+      <c r="K536" s="7">
+        <f t="shared" si="3"/>
+        <v>47171</v>
+      </c>
+    </row>
+    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A537" s="10" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B537" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C537" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D537" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E537" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F537" s="10" t="s">
+        <v>1512</v>
+      </c>
+      <c r="G537" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H537" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I537">
+        <v>2029</v>
+      </c>
+      <c r="J537" s="3">
+        <v>536</v>
+      </c>
+      <c r="K537" s="7">
+        <f t="shared" si="3"/>
+        <v>47178</v>
+      </c>
+    </row>
+    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A538" s="10" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B538" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C538" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D538" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E538" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F538" s="10" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G538" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H538" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I538">
+        <v>2029</v>
+      </c>
+      <c r="J538" s="3">
+        <v>537</v>
+      </c>
+      <c r="K538" s="7">
+        <f t="shared" si="3"/>
+        <v>47185</v>
+      </c>
+    </row>
+    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A539" s="10" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B539" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C539" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D539" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E539" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F539" s="10" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G539" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H539" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I539">
+        <v>2029</v>
+      </c>
+      <c r="J539" s="3">
+        <v>538</v>
+      </c>
+      <c r="K539" s="7">
+        <f t="shared" si="3"/>
+        <v>47192</v>
+      </c>
+    </row>
+    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A540" s="10" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B540" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C540" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E540" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F540" s="10" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G540" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H540" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I540">
+        <v>2029</v>
+      </c>
+      <c r="J540" s="3">
+        <v>539</v>
+      </c>
+      <c r="K540" s="7">
+        <f t="shared" si="3"/>
+        <v>47199</v>
+      </c>
+    </row>
+    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A541" s="10" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B541" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="C541" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E541" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F541" s="10" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G541" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H541" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="I541">
+        <v>2029</v>
+      </c>
+      <c r="J541" s="3">
+        <v>540</v>
+      </c>
+      <c r="K541" s="7">
+        <f t="shared" si="3"/>
+        <v>47206</v>
+      </c>
+    </row>
+    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A542" s="10" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B542" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C542" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D542" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E542" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F542" s="10" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G542" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H542" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I542">
+        <v>2029</v>
+      </c>
+      <c r="J542" s="3">
+        <v>541</v>
+      </c>
+      <c r="K542" s="7">
+        <f t="shared" si="3"/>
+        <v>47213</v>
+      </c>
+    </row>
+    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A543" s="10" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B543" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C543" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E543" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F543" s="10" t="s">
+        <v>1524</v>
+      </c>
+      <c r="G543" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H543" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I543">
+        <v>2029</v>
+      </c>
+      <c r="J543" s="3">
+        <v>542</v>
+      </c>
+      <c r="K543" s="7">
+        <f t="shared" si="3"/>
+        <v>47220</v>
+      </c>
+    </row>
+    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A544" s="10" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B544" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C544" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E544" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F544" s="10" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G544" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H544" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I544">
+        <v>2029</v>
+      </c>
+      <c r="J544" s="3">
+        <v>543</v>
+      </c>
+      <c r="K544" s="7">
+        <f t="shared" si="3"/>
+        <v>47227</v>
+      </c>
+    </row>
+    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A545" s="10" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B545" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C545" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E545" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F545" s="10" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G545" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H545" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="I545">
+        <v>2029</v>
+      </c>
+      <c r="J545" s="3">
+        <v>544</v>
+      </c>
+      <c r="K545" s="7">
+        <f t="shared" si="3"/>
+        <v>47234</v>
+      </c>
+    </row>
+    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A546" s="10" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B546" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C546" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D546" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E546" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F546" s="10" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G546" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H546" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I546">
+        <v>2029</v>
+      </c>
+      <c r="J546" s="3">
+        <v>545</v>
+      </c>
+      <c r="K546" s="7">
+        <f t="shared" si="3"/>
+        <v>47241</v>
+      </c>
+    </row>
+    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A547" s="10" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B547" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C547" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E547" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F547" s="10" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G547" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H547" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I547">
+        <v>2029</v>
+      </c>
+      <c r="J547" s="3">
+        <v>546</v>
+      </c>
+      <c r="K547" s="7">
+        <f t="shared" si="3"/>
+        <v>47248</v>
+      </c>
+    </row>
+    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A548" s="10" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B548" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C548" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E548" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F548" s="10" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G548" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H548" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I548">
+        <v>2029</v>
+      </c>
+      <c r="J548" s="3">
+        <v>547</v>
+      </c>
+      <c r="K548" s="7">
+        <f t="shared" si="3"/>
+        <v>47255</v>
+      </c>
+    </row>
+    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A549" s="10" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B549" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C549" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E549" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F549" s="10" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G549" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H549" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I549">
+        <v>2029</v>
+      </c>
+      <c r="J549" s="3">
+        <v>548</v>
+      </c>
+      <c r="K549" s="7">
+        <f t="shared" si="3"/>
+        <v>47262</v>
+      </c>
+    </row>
+    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A550" s="10" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B550" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C550" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D550" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E550" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F550" s="10" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G550" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H550" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I550">
+        <v>2029</v>
+      </c>
+      <c r="J550" s="3">
+        <v>549</v>
+      </c>
+      <c r="K550" s="7">
+        <f t="shared" si="3"/>
+        <v>47269</v>
+      </c>
+    </row>
+    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A551" s="10" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B551" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C551" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D551" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E551" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F551" s="10" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G551" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H551" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I551">
+        <v>2029</v>
+      </c>
+      <c r="J551" s="3">
+        <v>550</v>
+      </c>
+      <c r="K551" s="7">
+        <f t="shared" si="3"/>
+        <v>47276</v>
+      </c>
+    </row>
+    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A552" s="10" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B552" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C552" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D552" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E552" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F552" s="10" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G552" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H552" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I552">
+        <v>2029</v>
+      </c>
+      <c r="J552" s="3">
+        <v>551</v>
+      </c>
+      <c r="K552" s="7">
+        <f t="shared" si="3"/>
+        <v>47283</v>
+      </c>
+    </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A553" s="10" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B553" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C553" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D553" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E553" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F553" s="10" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G553" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H553" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I553">
+        <v>2029</v>
+      </c>
+      <c r="J553" s="3">
+        <v>552</v>
+      </c>
+      <c r="K553" s="7">
+        <f t="shared" si="3"/>
+        <v>47290</v>
+      </c>
+    </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A554" s="10" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B554" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="C554" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D554" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E554" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F554" s="10" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G554" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H554" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="I554">
+        <v>2029</v>
+      </c>
+      <c r="J554" s="3">
+        <v>553</v>
+      </c>
+      <c r="K554" s="7">
+        <f t="shared" si="3"/>
+        <v>47297</v>
+      </c>
+    </row>
+    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A555" s="10" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B555" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C555" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D555" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E555" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F555" s="10" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G555" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H555" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I555">
+        <v>2030</v>
+      </c>
+      <c r="J555" s="3">
+        <v>554</v>
+      </c>
+      <c r="K555" s="7">
+        <f t="shared" si="3"/>
+        <v>47304</v>
+      </c>
+    </row>
+    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A556" s="10" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B556" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C556" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D556" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E556" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F556" s="10" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G556" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H556" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I556">
+        <v>2030</v>
+      </c>
+      <c r="J556" s="3">
+        <v>555</v>
+      </c>
+      <c r="K556" s="7">
+        <f t="shared" si="3"/>
+        <v>47311</v>
+      </c>
+    </row>
+    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A557" s="10" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B557" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C557" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D557" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E557" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F557" s="10" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G557" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H557" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I557">
+        <v>2030</v>
+      </c>
+      <c r="J557" s="3">
+        <v>556</v>
+      </c>
+      <c r="K557" s="7">
+        <f t="shared" si="3"/>
+        <v>47318</v>
+      </c>
+    </row>
+    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A558" s="10" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B558" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="C558" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D558" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E558" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F558" s="10" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G558" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H558" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I558">
+        <v>2030</v>
+      </c>
+      <c r="J558" s="3">
+        <v>557</v>
+      </c>
+      <c r="K558" s="7">
+        <f t="shared" si="3"/>
+        <v>47325</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A559" s="10" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B559" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C559" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D559" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E559" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F559" s="10" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G559" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H559" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I559">
+        <v>2030</v>
+      </c>
+      <c r="J559" s="3">
+        <v>558</v>
+      </c>
+      <c r="K559" s="7">
+        <f t="shared" si="3"/>
+        <v>47332</v>
+      </c>
+    </row>
+    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A560" s="10" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B560" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C560" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D560" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E560" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F560" s="10" t="s">
+        <v>1558</v>
+      </c>
+      <c r="G560" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H560" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I560">
+        <v>2030</v>
+      </c>
+      <c r="J560" s="3">
+        <v>559</v>
+      </c>
+      <c r="K560" s="7">
+        <f t="shared" si="3"/>
+        <v>47339</v>
+      </c>
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A561" s="10" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B561" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C561" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E561" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F561" s="10" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G561" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H561" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I561">
+        <v>2030</v>
+      </c>
+      <c r="J561" s="3">
+        <v>560</v>
+      </c>
+      <c r="K561" s="7">
+        <f t="shared" si="3"/>
+        <v>47346</v>
+      </c>
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A562" s="10" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B562" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C562" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D562" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E562" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F562" s="10" t="s">
+        <v>1562</v>
+      </c>
+      <c r="G562" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H562" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I562">
+        <v>2030</v>
+      </c>
+      <c r="J562" s="3">
+        <v>561</v>
+      </c>
+      <c r="K562" s="7">
+        <f t="shared" si="3"/>
+        <v>47353</v>
+      </c>
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A563" s="10" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B563" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="C563" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D563" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E563" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F563" s="10" t="s">
+        <v>1564</v>
+      </c>
+      <c r="G563" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H563" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I563">
+        <v>2030</v>
+      </c>
+      <c r="J563" s="3">
+        <v>562</v>
+      </c>
+      <c r="K563" s="7">
+        <f t="shared" si="3"/>
+        <v>47360</v>
+      </c>
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A564" s="10" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B564" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C564" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D564" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E564" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F564" s="10" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G564" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H564" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I564">
+        <v>2030</v>
+      </c>
+      <c r="J564" s="3">
+        <v>563</v>
+      </c>
+      <c r="K564" s="7">
+        <f t="shared" si="3"/>
+        <v>47367</v>
+      </c>
+    </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A565" s="10" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B565" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C565" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D565" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E565" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F565" s="10" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G565" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H565" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I565">
+        <v>2030</v>
+      </c>
+      <c r="J565" s="3">
+        <v>564</v>
+      </c>
+      <c r="K565" s="7">
+        <f t="shared" si="3"/>
+        <v>47374</v>
+      </c>
+    </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A566" s="10" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B566" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C566" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D566" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E566" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F566" s="10" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G566" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H566" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I566">
+        <v>2030</v>
+      </c>
+      <c r="J566" s="3">
+        <v>565</v>
+      </c>
+      <c r="K566" s="7">
+        <f t="shared" si="3"/>
+        <v>47381</v>
+      </c>
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A567" s="10" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B567" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="C567" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D567" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E567" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F567" s="10" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G567" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H567" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I567">
+        <v>2030</v>
+      </c>
+      <c r="J567" s="3">
+        <v>566</v>
+      </c>
+      <c r="K567" s="7">
+        <f t="shared" si="3"/>
+        <v>47388</v>
+      </c>
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A568" s="10" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B568" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C568" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D568" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E568" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F568" s="10" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G568" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H568" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I568">
+        <v>2030</v>
+      </c>
+      <c r="J568" s="3">
+        <v>567</v>
+      </c>
+      <c r="K568" s="7">
+        <f t="shared" si="3"/>
+        <v>47395</v>
+      </c>
+    </row>
+    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A569" s="10" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B569" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C569" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D569" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E569" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F569" s="10" t="s">
+        <v>1576</v>
+      </c>
+      <c r="G569" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H569" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I569">
+        <v>2030</v>
+      </c>
+      <c r="J569" s="3">
+        <v>568</v>
+      </c>
+      <c r="K569" s="7">
+        <f t="shared" si="3"/>
+        <v>47402</v>
+      </c>
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A570" s="10" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B570" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C570" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D570" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E570" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F570" s="10" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G570" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H570" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I570">
+        <v>2030</v>
+      </c>
+      <c r="J570" s="3">
+        <v>569</v>
+      </c>
+      <c r="K570" s="7">
+        <f t="shared" si="3"/>
+        <v>47409</v>
+      </c>
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A571" s="10" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B571" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="C571" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E571" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F571" s="10" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G571" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H571" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I571">
+        <v>2030</v>
+      </c>
+      <c r="J571" s="3">
+        <v>570</v>
+      </c>
+      <c r="K571" s="7">
+        <f t="shared" si="3"/>
+        <v>47416</v>
+      </c>
+    </row>
+    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A572" s="10" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B572" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C572" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D572" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E572" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F572" s="10" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G572" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H572" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I572">
+        <v>2030</v>
+      </c>
+      <c r="J572" s="3">
+        <v>571</v>
+      </c>
+      <c r="K572" s="7">
+        <f t="shared" si="3"/>
+        <v>47423</v>
+      </c>
+    </row>
+    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A573" s="10" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B573" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C573" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D573" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E573" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F573" s="10" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G573" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H573" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I573">
+        <v>2030</v>
+      </c>
+      <c r="J573" s="3">
+        <v>572</v>
+      </c>
+      <c r="K573" s="7">
+        <f t="shared" si="3"/>
+        <v>47430</v>
+      </c>
+    </row>
+    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A574" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B574" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C574" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D574" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E574" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F574" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G574" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H574" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I574">
+        <v>2030</v>
+      </c>
+      <c r="J574" s="3">
+        <v>573</v>
+      </c>
+      <c r="K574" s="7">
+        <f t="shared" si="3"/>
+        <v>47437</v>
+      </c>
+    </row>
+    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A575" s="10" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B575" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C575" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D575" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E575" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F575" s="10" t="s">
+        <v>1588</v>
+      </c>
+      <c r="G575" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H575" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I575">
+        <v>2030</v>
+      </c>
+      <c r="J575" s="3">
+        <v>574</v>
+      </c>
+      <c r="K575" s="7">
+        <f t="shared" si="3"/>
+        <v>47444</v>
+      </c>
+    </row>
+    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A576" s="10" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B576" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C576" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D576" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E576" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F576" s="10" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G576" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H576" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I576">
+        <v>2030</v>
+      </c>
+      <c r="J576" s="3">
+        <v>575</v>
+      </c>
+      <c r="K576" s="7">
+        <f t="shared" si="3"/>
+        <v>47451</v>
+      </c>
+    </row>
+    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A577" s="10" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B577" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C577" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D577" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E577" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F577" s="10" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G577" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H577" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I577">
+        <v>2030</v>
+      </c>
+      <c r="J577" s="3">
+        <v>576</v>
+      </c>
+      <c r="K577" s="7">
+        <f t="shared" si="3"/>
+        <v>47458</v>
+      </c>
+    </row>
+    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A578" s="10" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B578" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C578" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D578" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E578" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F578" s="10" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G578" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H578" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I578">
+        <v>2030</v>
+      </c>
+      <c r="J578" s="3">
+        <v>577</v>
+      </c>
+      <c r="K578" s="7">
+        <f t="shared" ref="K578:K580" si="4">+K577+7</f>
+        <v>47465</v>
+      </c>
+    </row>
+    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A579" s="10" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B579" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C579" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D579" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E579" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F579" s="10" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G579" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H579" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I579">
+        <v>2030</v>
+      </c>
+      <c r="J579" s="3">
+        <v>578</v>
+      </c>
+      <c r="K579" s="7">
+        <f t="shared" si="4"/>
+        <v>47472</v>
+      </c>
+    </row>
+    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A580" s="10" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B580" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="C580" s="3">
+        <v>2028</v>
+      </c>
+      <c r="D580" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E580" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F580" s="10" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G580" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H580" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I580">
+        <v>2030</v>
+      </c>
+      <c r="J580" s="3">
+        <v>579</v>
+      </c>
+      <c r="K580" s="7">
+        <f t="shared" si="4"/>
+        <v>47479</v>
+      </c>
+    </row>
+    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K581" s="7"/>
+    </row>
+    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K582" s="7"/>
+    </row>
+    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K583" s="7"/>
+    </row>
+    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K584" s="7"/>
+    </row>
+    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K585" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A319 A425:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  <conditionalFormatting sqref="A581:A1048576 A1:A319">
+    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A320:A424">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F304 F320:F1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  <conditionalFormatting sqref="F1:F304 F320:F424 F426:F1048576">
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F305:F319">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A320:A580">
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F425:F580">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
